--- a/DateBase/orders/Dang Nguyen 195_2026-10-27.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-27.xlsx
@@ -1076,6 +1076,9 @@
       <c r="G2" t="str">
         <v>0201051511655815151515333102058105101015151515301515151015188771578101031536101515155105105103105555851555</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
